--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_nuble.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_nuble.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>27.17278706164829</v>
+      </c>
+      <c r="C2">
         <v>33.50946365906736</v>
-      </c>
-      <c r="C2">
-        <v>27.17278706164829</v>
       </c>
       <c r="D2">
         <v>2.984231589542045</v>
       </c>
       <c r="E2">
+        <v>16.91088277626739</v>
+      </c>
+      <c r="F2">
+        <v>62.23462737885814</v>
+      </c>
+      <c r="G2">
         <v>20.85448984487446</v>
-      </c>
-      <c r="F2">
-        <v>62.23462737885815</v>
-      </c>
-      <c r="G2">
-        <v>16.91088277626739</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>28.96435776731674</v>
+      </c>
+      <c r="C3">
         <v>40.59179556153329</v>
-      </c>
-      <c r="C3">
-        <v>28.96435776731674</v>
       </c>
       <c r="D3">
         <v>2.463552021206097</v>
       </c>
       <c r="E3">
-        <v>23.94003093642169</v>
+        <v>17.08245746242018</v>
       </c>
       <c r="F3">
         <v>58.97751160115813</v>
       </c>
       <c r="G3">
-        <v>17.08245746242018</v>
+        <v>23.94003093642169</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>25.59935503033903</v>
+      </c>
+      <c r="C4">
         <v>26.57953918615013</v>
-      </c>
-      <c r="C4">
-        <v>25.59935503033903</v>
       </c>
       <c r="D4">
         <v>3.762292464878672</v>
       </c>
       <c r="E4">
-        <v>17.46598260093687</v>
+        <v>16.82188266785635</v>
       </c>
       <c r="F4">
         <v>65.71213473120677</v>
       </c>
       <c r="G4">
-        <v>16.82188266785635</v>
+        <v>17.46598260093687</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>27.28896297178235</v>
+      </c>
+      <c r="C5">
         <v>39.57614001666865</v>
-      </c>
-      <c r="C5">
-        <v>27.28896297178235</v>
       </c>
       <c r="D5">
         <v>2.526774969915764</v>
       </c>
       <c r="E5">
+        <v>16.35390652871923</v>
+      </c>
+      <c r="F5">
+        <v>59.92864787727436</v>
+      </c>
+      <c r="G5">
         <v>23.71744559400642</v>
-      </c>
-      <c r="F5">
-        <v>59.92864787727434</v>
-      </c>
-      <c r="G5">
-        <v>16.35390652871923</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.33844678811122</v>
+      </c>
+      <c r="C6">
         <v>40.07670182166827</v>
-      </c>
-      <c r="C6">
-        <v>29.33844678811122</v>
       </c>
       <c r="D6">
         <v>2.495215311004785</v>
       </c>
       <c r="E6">
-        <v>23.65591397849462</v>
+        <v>17.31748726655348</v>
       </c>
       <c r="F6">
-        <v>59.02659875495189</v>
+        <v>59.02659875495191</v>
       </c>
       <c r="G6">
-        <v>17.31748726655348</v>
+        <v>23.65591397849463</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>25.05733944954128</v>
+      </c>
+      <c r="C7">
         <v>41.35321100917431</v>
-      </c>
-      <c r="C7">
-        <v>25.05733944954128</v>
       </c>
       <c r="D7">
         <v>2.418191902384914</v>
       </c>
       <c r="E7">
-        <v>24.85011370684309</v>
+        <v>15.05754255392461</v>
       </c>
       <c r="F7">
         <v>60.09234373923231</v>
       </c>
       <c r="G7">
-        <v>15.05754255392461</v>
+        <v>24.85011370684309</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>26.7682437850842</v>
+      </c>
+      <c r="C8">
         <v>46.9206094627105</v>
-      </c>
-      <c r="C8">
-        <v>26.7682437850842</v>
       </c>
       <c r="D8">
         <v>2.131259613741241</v>
       </c>
       <c r="E8">
-        <v>27.01417424627176</v>
+        <v>15.41160718408052</v>
       </c>
       <c r="F8">
         <v>57.57421856964773</v>
       </c>
       <c r="G8">
-        <v>15.41160718408052</v>
+        <v>27.01417424627176</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>27.4742995363838</v>
+      </c>
+      <c r="C9">
         <v>43.15662164886112</v>
-      </c>
-      <c r="C9">
-        <v>27.4742995363838</v>
       </c>
       <c r="D9">
         <v>2.317141522652966</v>
       </c>
       <c r="E9">
-        <v>25.29238038984052</v>
+        <v>16.1015948021264</v>
       </c>
       <c r="F9">
         <v>58.60602480803308</v>
       </c>
       <c r="G9">
-        <v>16.1015948021264</v>
+        <v>25.29238038984052</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>28.4129323047586</v>
+      </c>
+      <c r="C10">
         <v>40.3137730779232</v>
-      </c>
-      <c r="C10">
-        <v>28.4129323047586</v>
       </c>
       <c r="D10">
         <v>2.480541818963664</v>
       </c>
       <c r="E10">
-        <v>23.8929415390938</v>
+        <v>16.83961779512997</v>
       </c>
       <c r="F10">
         <v>59.26744066577622</v>
       </c>
       <c r="G10">
-        <v>16.83961779512997</v>
+        <v>23.8929415390938</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>26.13864030987044</v>
+      </c>
+      <c r="C11">
         <v>44.20996393749165</v>
-      </c>
-      <c r="C11">
-        <v>26.13864030987044</v>
       </c>
       <c r="D11">
         <v>2.261933534743203</v>
       </c>
       <c r="E11">
-        <v>25.95264230829543</v>
+        <v>15.34420573937588</v>
       </c>
       <c r="F11">
         <v>58.70315195232868</v>
       </c>
       <c r="G11">
-        <v>15.34420573937588</v>
+        <v>25.95264230829543</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>25.82824059183017</v>
+      </c>
+      <c r="C12">
         <v>54.45480862013509</v>
-      </c>
-      <c r="C12">
-        <v>25.82824059183017</v>
       </c>
       <c r="D12">
         <v>1.836385115180154</v>
       </c>
       <c r="E12">
-        <v>30.20517395182873</v>
+        <v>14.32649420160571</v>
       </c>
       <c r="F12">
         <v>55.46833184656557</v>
       </c>
       <c r="G12">
-        <v>14.32649420160571</v>
+        <v>30.20517395182873</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>26.7152342309111</v>
+      </c>
+      <c r="C13">
         <v>42.87163408336407</v>
-      </c>
-      <c r="C13">
-        <v>26.7152342309111</v>
       </c>
       <c r="D13">
         <v>2.332544633254463</v>
       </c>
       <c r="E13">
-        <v>25.2800435019032</v>
+        <v>15.75312669929309</v>
       </c>
       <c r="F13">
         <v>58.96682979880369</v>
       </c>
       <c r="G13">
-        <v>15.75312669929309</v>
+        <v>25.2800435019032</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>24.31947352677236</v>
+      </c>
+      <c r="C14">
         <v>51.1815734370326</v>
-      </c>
-      <c r="C14">
-        <v>24.31947352677236</v>
       </c>
       <c r="D14">
         <v>1.953828170660433</v>
       </c>
       <c r="E14">
-        <v>29.16311573206068</v>
+        <v>13.85716720640873</v>
       </c>
       <c r="F14">
         <v>56.9797170615306</v>
       </c>
       <c r="G14">
-        <v>13.85716720640873</v>
+        <v>29.16311573206068</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>24.0784084259801</v>
+      </c>
+      <c r="C15">
         <v>48.97600936220012</v>
-      </c>
-      <c r="C15">
-        <v>24.0784084259801</v>
       </c>
       <c r="D15">
         <v>2.041816009557945</v>
       </c>
       <c r="E15">
-        <v>28.30092983939138</v>
+        <v>13.91377852916315</v>
       </c>
       <c r="F15">
         <v>57.78529163144548</v>
       </c>
       <c r="G15">
-        <v>13.91377852916315</v>
+        <v>28.30092983939138</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>34.23672566371682</v>
+      </c>
+      <c r="C16">
         <v>35.23230088495576</v>
-      </c>
-      <c r="C16">
-        <v>34.23672566371682</v>
       </c>
       <c r="D16">
         <v>2.838304552590267</v>
       </c>
       <c r="E16">
-        <v>20.78981723237598</v>
+        <v>20.2023498694517</v>
       </c>
       <c r="F16">
         <v>59.00783289817232</v>
       </c>
       <c r="G16">
-        <v>20.2023498694517</v>
+        <v>20.78981723237598</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>30.44702569517775</v>
+      </c>
+      <c r="C17">
         <v>49.13762759591693</v>
-      </c>
-      <c r="C17">
-        <v>30.44702569517775</v>
       </c>
       <c r="D17">
         <v>2.035100286532951</v>
       </c>
       <c r="E17">
-        <v>27.36181889455115</v>
+        <v>16.95413563308506</v>
       </c>
       <c r="F17">
         <v>55.68404547236378</v>
       </c>
       <c r="G17">
-        <v>16.95413563308506</v>
+        <v>27.36181889455115</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>27.39553520320549</v>
+      </c>
+      <c r="C18">
         <v>39.76244991413853</v>
-      </c>
-      <c r="C18">
-        <v>27.39553520320549</v>
       </c>
       <c r="D18">
         <v>2.514935579068596</v>
       </c>
       <c r="E18">
-        <v>23.78734697371801</v>
+        <v>16.3890077904289</v>
       </c>
       <c r="F18">
         <v>59.82364523585309</v>
       </c>
       <c r="G18">
-        <v>16.3890077904289</v>
+        <v>23.78734697371801</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>28.67298578199052</v>
+      </c>
+      <c r="C19">
         <v>33.61158983196898</v>
-      </c>
-      <c r="C19">
-        <v>28.67298578199052</v>
       </c>
       <c r="D19">
         <v>2.975164236500561</v>
       </c>
       <c r="E19">
-        <v>20.71151229548999</v>
+        <v>17.66833703912654</v>
       </c>
       <c r="F19">
         <v>61.62015066538346</v>
       </c>
       <c r="G19">
-        <v>17.66833703912654</v>
+        <v>20.71151229548999</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>34.18774966711052</v>
+      </c>
+      <c r="C20">
         <v>23.66844207723036</v>
-      </c>
-      <c r="C20">
-        <v>34.18774966711052</v>
       </c>
       <c r="D20">
         <v>4.225035161744023</v>
       </c>
       <c r="E20">
-        <v>14.99367355546183</v>
+        <v>21.65752846900042</v>
       </c>
       <c r="F20">
         <v>63.34879797553774</v>
       </c>
       <c r="G20">
-        <v>21.65752846900042</v>
+        <v>14.99367355546183</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>27.74338773213281</v>
+      </c>
+      <c r="C21">
         <v>39.39223410241981</v>
-      </c>
-      <c r="C21">
-        <v>27.74338773213281</v>
       </c>
       <c r="D21">
         <v>2.538571428571429</v>
       </c>
       <c r="E21">
-        <v>23.56902356902356</v>
+        <v>16.5993265993266</v>
       </c>
       <c r="F21">
         <v>59.83164983164983</v>
       </c>
       <c r="G21">
-        <v>16.5993265993266</v>
+        <v>23.56902356902357</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>25.88376273217495</v>
+      </c>
+      <c r="C22">
         <v>38.61593768723787</v>
-      </c>
-      <c r="C22">
-        <v>25.88376273217495</v>
       </c>
       <c r="D22">
         <v>2.589604344453064</v>
       </c>
       <c r="E22">
-        <v>23.47477690766709</v>
+        <v>15.73483882717174</v>
       </c>
       <c r="F22">
         <v>60.79038426516117</v>
       </c>
       <c r="G22">
-        <v>15.73483882717174</v>
+        <v>23.47477690766709</v>
       </c>
     </row>
   </sheetData>
